--- a/public/modele-import-pharmapromo.xlsx
+++ b/public/modele-import-pharmapromo.xlsx
@@ -76,25 +76,25 @@
     <t>Prix promo</t>
   </si>
   <si>
-    <t>COMPLÉMENT ALIMENTAIRE</t>
-  </si>
-  <si>
-    <t>Chondro-Aid Fort ARKOPHARMA</t>
-  </si>
-  <si>
-    <t>Lot de 3 x 60 gélules</t>
+    <t>SOIN VISAGE</t>
+  </si>
+  <si>
+    <t>Eau Thermale AVÈNE Hydrance légère</t>
+  </si>
+  <si>
+    <t>Tube 40 ml</t>
   </si>
   <si>
     <t>A4</t>
   </si>
   <si>
-    <t>SOIN VISAGE</t>
-  </si>
-  <si>
-    <t>Crème hydratante AVÈNE</t>
-  </si>
-  <si>
-    <t>Tube 40 ml</t>
+    <t>CAPILLAIRE</t>
+  </si>
+  <si>
+    <t>Shampooing KLORANE à l’ortie blanche</t>
+  </si>
+  <si>
+    <t>Flacon 400 ml</t>
   </si>
   <si>
     <t>Vitrine</t>
@@ -103,22 +103,109 @@
     <t>HYGIÈNE BUCCO-DENTAIRE</t>
   </si>
   <si>
-    <t>Bain de bouche ELUDRIL</t>
+    <t>Dentifrice ELMEX Anti-caries</t>
+  </si>
+  <si>
+    <t>Tube 75 ml</t>
+  </si>
+  <si>
+    <t>Rayon</t>
+  </si>
+  <si>
+    <t>PHYTOTHÉRAPIE</t>
+  </si>
+  <si>
+    <t>Aboca Sollievo transit</t>
+  </si>
+  <si>
+    <t>90 comprimés</t>
+  </si>
+  <si>
+    <t>Petite</t>
+  </si>
+  <si>
+    <t>DRAINAGE</t>
+  </si>
+  <si>
+    <t>HERBESAN Draineur bio agrumes</t>
   </si>
   <si>
     <t>Flacon 500 ml</t>
   </si>
   <si>
-    <t>Rayon</t>
+    <t>Réglette</t>
+  </si>
+  <si>
+    <t>LUXÉOL Cheveux croissance et vitalité</t>
+  </si>
+  <si>
+    <t>60 gélules</t>
+  </si>
+  <si>
+    <t>ROGER &amp; GALLET Bois d’Orange gel douche</t>
+  </si>
+  <si>
+    <t>Flacon 200 ml</t>
+  </si>
+  <si>
+    <t>DIGESTION</t>
+  </si>
+  <si>
+    <t>PROBIOLOG Fort équilibre intestinal</t>
+  </si>
+  <si>
+    <t>30 gélules</t>
+  </si>
+  <si>
+    <t>SOMMEIL</t>
+  </si>
+  <si>
+    <t>SANTAROME Bio nuit tranquille</t>
+  </si>
+  <si>
+    <t>20 ampoules</t>
+  </si>
+  <si>
+    <t>MINCEUR</t>
+  </si>
+  <si>
+    <t>STC NUTRITION Draineur 5 actions</t>
+  </si>
+  <si>
+    <t>CIRCULATION</t>
+  </si>
+  <si>
+    <t>LES 3 CHÊNES Jambes légères confort</t>
+  </si>
+  <si>
+    <t>60 comprimés</t>
+  </si>
+  <si>
+    <t>PREMIERS SOINS</t>
+  </si>
+  <si>
+    <t>Pansements ELASTOPLAST résistants</t>
+  </si>
+  <si>
+    <t>Boîte de 20</t>
+  </si>
+  <si>
+    <t>CORPS</t>
+  </si>
+  <si>
+    <t>Huile de soin BI-OIL F/200ML</t>
+  </si>
+  <si>
+    <t>SOLAIRE</t>
+  </si>
+  <si>
+    <t>DAYLONG Sensitive lait solaire SPF50+</t>
   </si>
   <si>
     <t>Bon</t>
   </si>
   <si>
-    <t>HYGIÈNE</t>
-  </si>
-  <si>
-    <t>Dentifrice SENSODYNE</t>
+    <t>Bain de bouche MERIDOL protection gencives</t>
   </si>
   <si>
     <t>31/12/2026</t>
@@ -127,43 +214,124 @@
     <t>BÉBÉ</t>
   </si>
   <si>
-    <t>Lingettes MUSTELA</t>
+    <t>BIOLANE Lingettes à l’eau</t>
   </si>
   <si>
     <t>30/09/2026</t>
   </si>
   <si>
+    <t>VÉTÉRINAIRE</t>
+  </si>
+  <si>
+    <t>CLÉMENT THÉKAN antiparasitaire chien</t>
+  </si>
+  <si>
+    <t>15/11/2026</t>
+  </si>
+  <si>
+    <t>ANTI-POUX</t>
+  </si>
+  <si>
+    <t>POUXIT Lotion traitante</t>
+  </si>
+  <si>
+    <t>INCONTINENCE</t>
+  </si>
+  <si>
+    <t>Protections TENA Lady Discreet</t>
+  </si>
+  <si>
+    <t>31/10/2026</t>
+  </si>
+  <si>
+    <t>AUTODIAGNOSTIC</t>
+  </si>
+  <si>
+    <t>CLEARBLUE test de grossesse digital</t>
+  </si>
+  <si>
     <t>Lot</t>
   </si>
   <si>
-    <t>Magnésium B6 SANOFI</t>
-  </si>
-  <si>
-    <t>Lot de 3 boîtes</t>
-  </si>
-  <si>
-    <t>SOLAIRE</t>
-  </si>
-  <si>
-    <t>Spray solaire BIODERMA SPF50+</t>
+    <t>HYGIÈNE INTIME</t>
+  </si>
+  <si>
+    <t>Gel lavant SAFORELLE soin doux</t>
+  </si>
+  <si>
+    <t>Lot de 2 flacons</t>
+  </si>
+  <si>
+    <t>DAYLONG Spray solaire SPF30</t>
   </si>
   <si>
     <t>Lot de 2 sprays</t>
   </si>
   <si>
-    <t>Réglette</t>
+    <t>NEUTRADERM Gel douche surgras</t>
+  </si>
+  <si>
+    <t>IMMUNITÉ</t>
+  </si>
+  <si>
+    <t>SANTÉ VERTE Vitamine C acérola</t>
+  </si>
+  <si>
+    <t>Lot de 2 tubes</t>
+  </si>
+  <si>
+    <t>HYDRALIN Quotidien gel lavant</t>
+  </si>
+  <si>
+    <t>Shampooing DUCRAY Kertyol état pelliculaire</t>
+  </si>
+  <si>
+    <t>SOINS DES LÈVRES</t>
+  </si>
+  <si>
+    <t>LAINO Stick lèvres karité</t>
+  </si>
+  <si>
+    <t>Lot de 2 sticks</t>
+  </si>
+  <si>
+    <t>MICRONUTRITION</t>
+  </si>
+  <si>
+    <t>THALAMAG Magnésium marin fatigue</t>
+  </si>
+  <si>
+    <t>30 comprimés</t>
   </si>
   <si>
     <t>Multi</t>
   </si>
   <si>
-    <t>Savon LE PETIT MARSEILLAIS</t>
-  </si>
-  <si>
-    <t>Petite</t>
-  </si>
-  <si>
-    <t>Spray solaire GARNIER SPF50</t>
+    <t>PROTECTION AUDITIVE</t>
+  </si>
+  <si>
+    <t>QUIES Boules Quies cire naturelle</t>
+  </si>
+  <si>
+    <t>TEPE Brossettes interdentaires</t>
+  </si>
+  <si>
+    <t>ANTI-MOUSTIQUES</t>
+  </si>
+  <si>
+    <t>PARAKITO Recharges bracelet répulsif</t>
+  </si>
+  <si>
+    <t>SOIN DES ONGLES</t>
+  </si>
+  <si>
+    <t>MAVALA Vernis à ongles couleur</t>
+  </si>
+  <si>
+    <t>PAMPERS Baby-Dry taille 4 mégapack</t>
+  </si>
+  <si>
+    <t>IPHYM Tisane digestion bio</t>
   </si>
   <si>
     <t>2ᵉ produit</t>
@@ -172,19 +340,53 @@
     <t>DERMO-COSMÉTIQUE</t>
   </si>
   <si>
-    <t>Crème mains NEUTROGENA</t>
-  </si>
-  <si>
-    <t>Tube 75 ml</t>
-  </si>
-  <si>
-    <t>Bain de bouche LISTERINE</t>
+    <t>ROC Retinol Correxion crème nuit</t>
+  </si>
+  <si>
+    <t>Pot 30 ml</t>
+  </si>
+  <si>
+    <t>Bain de bouche CB12 haleine fraîche</t>
+  </si>
+  <si>
+    <t>Flacon 250 ml</t>
+  </si>
+  <si>
+    <t>ELANCYL Slim Design fermeté</t>
+  </si>
+  <si>
+    <t>Tube 200 ml</t>
+  </si>
+  <si>
+    <t>PIEDS</t>
+  </si>
+  <si>
+    <t>Crème anti-callosités AKILÉÏNE</t>
+  </si>
+  <si>
+    <t>JOWAÉ Crème lissante hydratante</t>
+  </si>
+  <si>
+    <t>Pot 40 ml</t>
+  </si>
+  <si>
+    <t>HOMME</t>
+  </si>
+  <si>
+    <t>EAU PRÉCIEUSE Lotion soin visage</t>
+  </si>
+  <si>
+    <t>Flacon 375 ml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="100" formatCode="#,##0.00"/>
+    <numFmt numFmtId="101" formatCode="0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <family val="2"/>
@@ -221,11 +423,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf/>
     <xf fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="100" applyNumberFormat="1"/>
+    <xf numFmtId="101" applyNumberFormat="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -236,20 +440,20 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
   </cols>
@@ -323,11 +527,11 @@
       <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="D2">
-        <v>31.9</v>
-      </c>
-      <c r="E2">
-        <v>26.9</v>
+      <c r="D2" s="2">
+        <v>19.9</v>
+      </c>
+      <c r="E2" s="2">
+        <v>14.9</v>
       </c>
       <c r="R2" t="s">
         <v>22</v>
@@ -346,11 +550,11 @@
       <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="D3">
-        <v>19.9</v>
-      </c>
-      <c r="E3">
-        <v>14.9</v>
+      <c r="D3" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="E3" s="2">
+        <v>6.9</v>
       </c>
       <c r="R3" t="s">
         <v>26</v>
@@ -369,11 +573,11 @@
       <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="D4">
-        <v>8.5</v>
-      </c>
-      <c r="E4">
-        <v>5.9</v>
+      <c r="D4" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3.9</v>
       </c>
       <c r="R4" t="s">
         <v>30</v>
@@ -384,27 +588,30 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="R5" t="s">
         <v>34</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="S5" t="s">
         <v>35</v>
-      </c>
-      <c r="S5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -412,176 +619,903 @@
       <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="F6">
-        <v>1.5</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="D6" s="2">
+        <v>18.9</v>
+      </c>
+      <c r="E6" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="R6" t="s">
         <v>38</v>
       </c>
       <c r="S6" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>19.98</v>
+      <c r="D7" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="E7" s="2">
+        <v>19.9</v>
       </c>
       <c r="R7" t="s">
         <v>41</v>
       </c>
       <c r="S7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="R8" t="s">
         <v>43</v>
       </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>24.9</v>
-      </c>
-      <c r="R8" t="s">
-        <v>44</v>
-      </c>
       <c r="S8" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>18.9</v>
+      </c>
+      <c r="R9" t="s">
         <v>46</v>
       </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>3.5</v>
-      </c>
-      <c r="M9">
-        <v>3</v>
-      </c>
-      <c r="N9">
-        <v>9</v>
-      </c>
-      <c r="O9">
-        <v>5</v>
-      </c>
-      <c r="P9">
-        <v>13.5</v>
-      </c>
       <c r="S9" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="E10" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="R10" t="s">
         <v>49</v>
       </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>12.9</v>
-      </c>
-      <c r="M10">
-        <v>2</v>
-      </c>
-      <c r="N10">
-        <v>22.9</v>
-      </c>
-      <c r="O10">
-        <v>3</v>
-      </c>
-      <c r="P10">
-        <v>29.9</v>
-      </c>
       <c r="S10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11">
-        <v>4.95</v>
-      </c>
-      <c r="Q11">
-        <v>50</v>
+      <c r="D11" s="2">
+        <v>22.9</v>
+      </c>
+      <c r="E11" s="2">
+        <v>17.5</v>
       </c>
       <c r="R11" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="S11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2">
+        <v>17.9</v>
+      </c>
+      <c r="E12" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="R12" t="s">
+        <v>54</v>
+      </c>
+      <c r="S12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="R13" t="s">
+        <v>57</v>
+      </c>
+      <c r="S13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="2">
+        <v>16.9</v>
+      </c>
+      <c r="E14" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="S14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="2">
+        <v>24.5</v>
+      </c>
+      <c r="E15" s="2">
+        <v>19.9</v>
+      </c>
+      <c r="R15" t="s">
+        <v>43</v>
+      </c>
+      <c r="S15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+      <c r="S17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="2">
+        <v>5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>70</v>
+      </c>
+      <c r="S18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="2">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>64</v>
+      </c>
+      <c r="S19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G20" t="s">
+        <v>75</v>
+      </c>
+      <c r="S20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="2">
+        <v>4</v>
+      </c>
+      <c r="G21" t="s">
+        <v>64</v>
+      </c>
+      <c r="S21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="R22" t="s">
+        <v>81</v>
+      </c>
+      <c r="S22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="R23" t="s">
+        <v>83</v>
+      </c>
+      <c r="S23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>9.8</v>
+      </c>
+      <c r="R24" t="s">
+        <v>81</v>
+      </c>
+      <c r="S24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="H25" s="3">
+        <v>2</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="R25" t="s">
+        <v>87</v>
+      </c>
+      <c r="S25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="R26" t="s">
+        <v>81</v>
+      </c>
+      <c r="S26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>2</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="R27" t="s">
+        <v>81</v>
+      </c>
+      <c r="S27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="R28" t="s">
+        <v>92</v>
+      </c>
+      <c r="S28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="2">
+        <v>19.9</v>
+      </c>
+      <c r="H29" s="3">
+        <v>2</v>
+      </c>
+      <c r="I29" s="3">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>19.9</v>
+      </c>
+      <c r="R29" t="s">
+        <v>95</v>
+      </c>
+      <c r="S29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="K30" s="3">
+        <v>1</v>
+      </c>
+      <c r="L30" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="M30" s="3">
+        <v>2</v>
+      </c>
+      <c r="N30" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="O30" s="3">
+        <v>3</v>
+      </c>
+      <c r="P30" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="S30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>99</v>
+      </c>
+      <c r="K31" s="3">
+        <v>1</v>
+      </c>
+      <c r="L31" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="M31" s="3">
+        <v>3</v>
+      </c>
+      <c r="N31" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="O31" s="3">
+        <v>5</v>
+      </c>
+      <c r="P31" s="3">
+        <v>21.9</v>
+      </c>
+      <c r="S31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>101</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1</v>
+      </c>
+      <c r="L32" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="M32" s="3">
+        <v>2</v>
+      </c>
+      <c r="N32" s="3">
+        <v>17.9</v>
+      </c>
+      <c r="O32" s="3">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
+        <v>24.9</v>
+      </c>
+      <c r="S32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+      <c r="K33" s="3">
+        <v>1</v>
+      </c>
+      <c r="L33" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="M33" s="3">
+        <v>2</v>
+      </c>
+      <c r="N33" s="3">
+        <v>11.9</v>
+      </c>
+      <c r="O33" s="3">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="S33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="K34" s="3">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3">
+        <v>11.9</v>
+      </c>
+      <c r="M34" s="3">
+        <v>2</v>
+      </c>
+      <c r="N34" s="3">
+        <v>21.9</v>
+      </c>
+      <c r="O34" s="3">
+        <v>3</v>
+      </c>
+      <c r="P34" s="3">
+        <v>29.9</v>
+      </c>
+      <c r="S34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+      <c r="K35" s="3">
+        <v>1</v>
+      </c>
+      <c r="L35" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="M35" s="3">
+        <v>2</v>
+      </c>
+      <c r="N35" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O35" s="3">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3">
+        <v>13.9</v>
+      </c>
+      <c r="S35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="2">
+        <v>32</v>
+      </c>
+      <c r="Q36" s="3">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
+      <c r="R36" t="s">
+        <v>109</v>
+      </c>
+      <c r="S36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12">
-        <v>6.5</v>
-      </c>
-      <c r="Q12">
-        <v>60</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>50</v>
+      </c>
+      <c r="R37" t="s">
+        <v>111</v>
+      </c>
+      <c r="S37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="2">
+        <v>28.9</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>40</v>
+      </c>
+      <c r="R38" t="s">
+        <v>113</v>
+      </c>
+      <c r="S38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>40</v>
+      </c>
+      <c r="R39" t="s">
         <v>30</v>
       </c>
-      <c r="S12" t="s">
-        <v>27</v>
+      <c r="S39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>50</v>
+      </c>
+      <c r="R40" t="s">
+        <v>117</v>
+      </c>
+      <c r="S40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>30</v>
+      </c>
+      <c r="R41" t="s">
+        <v>120</v>
+      </c>
+      <c r="S41" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
